--- a/fiba_wc_2023_boxscores.xlsx
+++ b/fiba_wc_2023_boxscores.xlsx
@@ -601,7 +601,7 @@
         <v>118.9</v>
       </c>
       <c r="R2" t="n">
-        <v>81.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="S2" t="n">
         <v>0.5137</v>
@@ -677,7 +677,7 @@
         <v>159.7</v>
       </c>
       <c r="R3" t="n">
-        <v>91.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="S3" t="n">
         <v>0.8429</v>
@@ -753,7 +753,7 @@
         <v>128.4</v>
       </c>
       <c r="R4" t="n">
-        <v>95.3</v>
+        <v>98.3</v>
       </c>
       <c r="S4" t="n">
         <v>0.6081</v>
@@ -829,7 +829,7 @@
         <v>99.3</v>
       </c>
       <c r="R5" t="n">
-        <v>105.4</v>
+        <v>106.2</v>
       </c>
       <c r="S5" t="n">
         <v>0.3968</v>
@@ -905,7 +905,7 @@
         <v>115.8</v>
       </c>
       <c r="R6" t="n">
-        <v>111.8</v>
+        <v>112.1</v>
       </c>
       <c r="S6" t="n">
         <v>0.5877</v>
@@ -981,7 +981,7 @@
         <v>134.2</v>
       </c>
       <c r="R7" t="n">
-        <v>119.4</v>
+        <v>118</v>
       </c>
       <c r="S7" t="n">
         <v>0.5984</v>
@@ -1057,7 +1057,7 @@
         <v>114.9</v>
       </c>
       <c r="R8" t="n">
-        <v>126.9</v>
+        <v>125.3</v>
       </c>
       <c r="S8" t="n">
         <v>0.5714</v>
@@ -1133,7 +1133,7 @@
         <v>131.9</v>
       </c>
       <c r="R9" t="n">
-        <v>122.5</v>
+        <v>121.5</v>
       </c>
       <c r="S9" t="n">
         <v>0.6131</v>
@@ -1209,7 +1209,7 @@
         <v>105.2</v>
       </c>
       <c r="R10" t="n">
-        <v>81.90000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="S10" t="n">
         <v>0.5139</v>
@@ -1285,7 +1285,7 @@
         <v>113.9</v>
       </c>
       <c r="R11" t="n">
-        <v>109.9</v>
+        <v>113.9</v>
       </c>
       <c r="S11" t="n">
         <v>0.5984</v>
@@ -1361,7 +1361,7 @@
         <v>138.3</v>
       </c>
       <c r="R12" t="n">
-        <v>102.7</v>
+        <v>107.9</v>
       </c>
       <c r="S12" t="n">
         <v>0.6544</v>
@@ -1437,7 +1437,7 @@
         <v>128.2</v>
       </c>
       <c r="R13" t="n">
-        <v>93.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>0.6825</v>
@@ -1513,7 +1513,7 @@
         <v>132.5</v>
       </c>
       <c r="R14" t="n">
-        <v>94.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="S14" t="n">
         <v>0.6641</v>
@@ -1589,7 +1589,7 @@
         <v>110.4</v>
       </c>
       <c r="R15" t="n">
-        <v>107.7</v>
+        <v>107.6</v>
       </c>
       <c r="S15" t="n">
         <v>0.4571</v>
@@ -1665,7 +1665,7 @@
         <v>136.7</v>
       </c>
       <c r="R16" t="n">
-        <v>134.3</v>
+        <v>141.2</v>
       </c>
       <c r="S16" t="n">
         <v>0.669</v>
@@ -1741,7 +1741,7 @@
         <v>118.6</v>
       </c>
       <c r="R17" t="n">
-        <v>110</v>
+        <v>109.4</v>
       </c>
       <c r="S17" t="n">
         <v>0.5545</v>
@@ -1817,7 +1817,7 @@
         <v>137.6</v>
       </c>
       <c r="R18" t="n">
-        <v>82.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="S18" t="n">
         <v>0.6864</v>
@@ -1893,7 +1893,7 @@
         <v>118.6</v>
       </c>
       <c r="R19" t="n">
-        <v>97.2</v>
+        <v>96.2</v>
       </c>
       <c r="S19" t="n">
         <v>0.5821</v>
@@ -1969,7 +1969,7 @@
         <v>152.4</v>
       </c>
       <c r="R20" t="n">
-        <v>110</v>
+        <v>107.8</v>
       </c>
       <c r="S20" t="n">
         <v>0.7426</v>
@@ -2045,7 +2045,7 @@
         <v>102.6</v>
       </c>
       <c r="R21" t="n">
-        <v>105.3</v>
+        <v>106</v>
       </c>
       <c r="S21" t="n">
         <v>0.4224</v>
@@ -2121,7 +2121,7 @@
         <v>134.9</v>
       </c>
       <c r="R22" t="n">
-        <v>95.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="S22" t="n">
         <v>0.7121</v>
@@ -2197,7 +2197,7 @@
         <v>130</v>
       </c>
       <c r="R23" t="n">
-        <v>101.6</v>
+        <v>100.6</v>
       </c>
       <c r="S23" t="n">
         <v>0.625</v>
@@ -2273,7 +2273,7 @@
         <v>125.3</v>
       </c>
       <c r="R24" t="n">
-        <v>113.5</v>
+        <v>114.8</v>
       </c>
       <c r="S24" t="n">
         <v>0.6983</v>
@@ -2349,7 +2349,7 @@
         <v>109.4</v>
       </c>
       <c r="R25" t="n">
-        <v>118</v>
+        <v>118.6</v>
       </c>
       <c r="S25" t="n">
         <v>0.4919</v>
@@ -2425,7 +2425,7 @@
         <v>116.6</v>
       </c>
       <c r="R26" t="n">
-        <v>84.8</v>
+        <v>79.7</v>
       </c>
       <c r="S26" t="n">
         <v>0.661</v>
@@ -2501,7 +2501,7 @@
         <v>141.6</v>
       </c>
       <c r="R27" t="n">
-        <v>105.2</v>
+        <v>98.8</v>
       </c>
       <c r="S27" t="n">
         <v>0.6475</v>
@@ -2577,7 +2577,7 @@
         <v>119.2</v>
       </c>
       <c r="R28" t="n">
-        <v>67.2</v>
+        <v>69.3</v>
       </c>
       <c r="S28" t="n">
         <v>0.55</v>
@@ -2653,7 +2653,7 @@
         <v>106</v>
       </c>
       <c r="R29" t="n">
-        <v>91</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S29" t="n">
         <v>0.5159</v>
@@ -2729,7 +2729,7 @@
         <v>121.8</v>
       </c>
       <c r="R30" t="n">
-        <v>128.9</v>
+        <v>129.4</v>
       </c>
       <c r="S30" t="n">
         <v>0.6096</v>
@@ -2805,7 +2805,7 @@
         <v>118.2</v>
       </c>
       <c r="R31" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="S31" t="n">
         <v>0.6642</v>
@@ -2881,7 +2881,7 @@
         <v>141.3</v>
       </c>
       <c r="R32" t="n">
-        <v>143.8</v>
+        <v>136.6</v>
       </c>
       <c r="S32" t="n">
         <v>0.6768999999999999</v>
@@ -2957,7 +2957,7 @@
         <v>121.5</v>
       </c>
       <c r="R33" t="n">
-        <v>130.8</v>
+        <v>131.9</v>
       </c>
       <c r="S33" t="n">
         <v>0.5802</v>
